--- a/backend/demo-data/current/DiskAlani_20260901000000.xlsx
+++ b/backend/demo-data/current/DiskAlani_20260901000000.xlsx
@@ -403,26 +403,86 @@
       <c r="A1" t="str">
         <v>Rapor</v>
       </c>
+      <c r="B1" t="str">
+        <v/>
+      </c>
+      <c r="C1" t="str">
+        <v/>
+      </c>
+      <c r="D1" t="str">
+        <v/>
+      </c>
+      <c r="E1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
         <v/>
       </c>
+      <c r="B2" t="str">
+        <v/>
+      </c>
+      <c r="C2" t="str">
+        <v/>
+      </c>
+      <c r="D2" t="str">
+        <v/>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
         <v/>
       </c>
+      <c r="B3" t="str">
+        <v/>
+      </c>
+      <c r="C3" t="str">
+        <v/>
+      </c>
+      <c r="D3" t="str">
+        <v/>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
         <v/>
       </c>
+      <c r="B4" t="str">
+        <v/>
+      </c>
+      <c r="C4" t="str">
+        <v/>
+      </c>
+      <c r="D4" t="str">
+        <v/>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
         <v/>
       </c>
+      <c r="B5" t="str">
+        <v/>
+      </c>
+      <c r="C5" t="str">
+        <v/>
+      </c>
+      <c r="D5" t="str">
+        <v/>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -443,7 +503,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>SYNHOST00000</v>
+        <v>IST3x05</v>
       </c>
       <c r="B7" t="str">
         <v>C</v>
@@ -455,12 +515,12 @@
         <v>263168</v>
       </c>
       <c r="E7" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>SYNHOST00001</v>
+        <v>SAW3x05</v>
       </c>
       <c r="B8" t="str">
         <v>C</v>
@@ -472,12 +532,12 @@
         <v>394240</v>
       </c>
       <c r="E8" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>SYNHOST00002</v>
+        <v>ESB3x05</v>
       </c>
       <c r="B9" t="str">
         <v>C</v>
@@ -489,12 +549,12 @@
         <v>446464</v>
       </c>
       <c r="E9" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>SYNHOST00003</v>
+        <v>ADB3x05</v>
       </c>
       <c r="B10" t="str">
         <v>C</v>
@@ -506,12 +566,12 @@
         <v>214016</v>
       </c>
       <c r="E10" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>SYNHOST00004</v>
+        <v>AYT3x05</v>
       </c>
       <c r="B11" t="str">
         <v>C</v>
@@ -523,12 +583,12 @@
         <v>242688</v>
       </c>
       <c r="E11" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>SYNHOST00005</v>
+        <v>ADA3x05</v>
       </c>
       <c r="B12" t="str">
         <v>C</v>
@@ -540,12 +600,12 @@
         <v>227328</v>
       </c>
       <c r="E12" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>SYNHOST00006</v>
+        <v>TZX3x05</v>
       </c>
       <c r="B13" t="str">
         <v>C</v>
@@ -557,12 +617,12 @@
         <v>418816</v>
       </c>
       <c r="E13" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>SYNHOST00007</v>
+        <v>GZT3x05</v>
       </c>
       <c r="B14" t="str">
         <v>C</v>
@@ -574,12 +634,12 @@
         <v>461824</v>
       </c>
       <c r="E14" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>SYNHOST00008</v>
+        <v>KYA3x05</v>
       </c>
       <c r="B15" t="str">
         <v>C</v>
@@ -591,12 +651,12 @@
         <v>487424</v>
       </c>
       <c r="E15" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>SYNHOST00009</v>
+        <v>VAN3x05</v>
       </c>
       <c r="B16" t="str">
         <v>C</v>
@@ -608,12 +668,12 @@
         <v>311296</v>
       </c>
       <c r="E16" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>SYNHOST00010</v>
+        <v>JFK3x05</v>
       </c>
       <c r="B17" t="str">
         <v>C</v>
@@ -625,12 +685,12 @@
         <v>387072</v>
       </c>
       <c r="E17" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>SYNHOST00011</v>
+        <v>ORD3x05</v>
       </c>
       <c r="B18" t="str">
         <v>C</v>
@@ -642,12 +702,12 @@
         <v>207872</v>
       </c>
       <c r="E18" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>SYNHOST00012</v>
+        <v>IAD3x05</v>
       </c>
       <c r="B19" t="str">
         <v>C</v>
@@ -659,12 +719,12 @@
         <v>251904</v>
       </c>
       <c r="E19" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>SYNHOST00013</v>
+        <v>LAX3x05</v>
       </c>
       <c r="B20" t="str">
         <v>C</v>
@@ -676,12 +736,12 @@
         <v>253952</v>
       </c>
       <c r="E20" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>SYNHOST00014</v>
+        <v>MIA3x05</v>
       </c>
       <c r="B21" t="str">
         <v>C</v>
@@ -693,12 +753,12 @@
         <v>243712</v>
       </c>
       <c r="E21" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>SYNHOST00015</v>
+        <v>BOS3x05</v>
       </c>
       <c r="B22" t="str">
         <v>C</v>
@@ -710,12 +770,12 @@
         <v>302080</v>
       </c>
       <c r="E22" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>SYNHOST00016</v>
+        <v>LHR3x05</v>
       </c>
       <c r="B23" t="str">
         <v>C</v>
@@ -727,12 +787,12 @@
         <v>381952</v>
       </c>
       <c r="E23" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>SYNHOST00017</v>
+        <v>CDG3x05</v>
       </c>
       <c r="B24" t="str">
         <v>C</v>
@@ -744,12 +804,12 @@
         <v>468992</v>
       </c>
       <c r="E24" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>SYNHOST00018</v>
+        <v>FRA3x05</v>
       </c>
       <c r="B25" t="str">
         <v>C</v>
@@ -761,12 +821,12 @@
         <v>378880</v>
       </c>
       <c r="E25" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>SYNHOST00019</v>
+        <v>AMS3x05</v>
       </c>
       <c r="B26" t="str">
         <v>C</v>
@@ -778,12 +838,12 @@
         <v>434176</v>
       </c>
       <c r="E26" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>SYNHOST00020</v>
+        <v>MAD3x05</v>
       </c>
       <c r="B27" t="str">
         <v>C</v>
@@ -795,12 +855,12 @@
         <v>355328</v>
       </c>
       <c r="E27" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>SYNHOST00021</v>
+        <v>FCO3x05</v>
       </c>
       <c r="B28" t="str">
         <v>C</v>
@@ -812,12 +872,12 @@
         <v>463872</v>
       </c>
       <c r="E28" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>SYNHOST00022</v>
+        <v>MUC3x05</v>
       </c>
       <c r="B29" t="str">
         <v>C</v>
@@ -829,12 +889,12 @@
         <v>211968</v>
       </c>
       <c r="E29" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>SYNHOST00023</v>
+        <v>ZRH3x05</v>
       </c>
       <c r="B30" t="str">
         <v>C</v>
@@ -846,12 +906,12 @@
         <v>281600</v>
       </c>
       <c r="E30" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>SYNHOST00024</v>
+        <v>VIE3x05</v>
       </c>
       <c r="B31" t="str">
         <v>C</v>
@@ -863,12 +923,12 @@
         <v>453632</v>
       </c>
       <c r="E31" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>SYNHOST00025</v>
+        <v>BRU3x05</v>
       </c>
       <c r="B32" t="str">
         <v>C</v>
@@ -880,12 +940,12 @@
         <v>215040</v>
       </c>
       <c r="E32" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>SYNHOST00026</v>
+        <v>CPH3x05</v>
       </c>
       <c r="B33" t="str">
         <v>C</v>
@@ -897,12 +957,12 @@
         <v>460800</v>
       </c>
       <c r="E33" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>SYNHOST00027</v>
+        <v>ARN3x05</v>
       </c>
       <c r="B34" t="str">
         <v>C</v>
@@ -914,12 +974,12 @@
         <v>492544</v>
       </c>
       <c r="E34" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>SYNHOST00028</v>
+        <v>OSL3x05</v>
       </c>
       <c r="B35" t="str">
         <v>C</v>
@@ -931,12 +991,12 @@
         <v>253952</v>
       </c>
       <c r="E35" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>SYNHOST00029</v>
+        <v>WAW3x05</v>
       </c>
       <c r="B36" t="str">
         <v>C</v>
@@ -948,12 +1008,12 @@
         <v>480256</v>
       </c>
       <c r="E36" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>SYNHOST00030</v>
+        <v>PRG3x05</v>
       </c>
       <c r="B37" t="str">
         <v>C</v>
@@ -965,12 +1025,12 @@
         <v>473088</v>
       </c>
       <c r="E37" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>SYNHOST00031</v>
+        <v>BUD3x05</v>
       </c>
       <c r="B38" t="str">
         <v>C</v>
@@ -982,12 +1042,12 @@
         <v>460800</v>
       </c>
       <c r="E38" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>SYNHOST00032</v>
+        <v>DXB3x05</v>
       </c>
       <c r="B39" t="str">
         <v>C</v>
@@ -999,12 +1059,12 @@
         <v>248832</v>
       </c>
       <c r="E39" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>SYNHOST00033</v>
+        <v>DOH3x05</v>
       </c>
       <c r="B40" t="str">
         <v>C</v>
@@ -1016,12 +1076,12 @@
         <v>303104</v>
       </c>
       <c r="E40" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>SYNHOST00034</v>
+        <v>JED3x05</v>
       </c>
       <c r="B41" t="str">
         <v>C</v>
@@ -1033,12 +1093,12 @@
         <v>510976</v>
       </c>
       <c r="E41" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>SYNHOST00035</v>
+        <v>CAI3x05</v>
       </c>
       <c r="B42" t="str">
         <v>C</v>
@@ -1050,12 +1110,12 @@
         <v>406528</v>
       </c>
       <c r="E42" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>SYNHOST00036</v>
+        <v>ALG3x05</v>
       </c>
       <c r="B43" t="str">
         <v>C</v>
@@ -1067,12 +1127,12 @@
         <v>289792</v>
       </c>
       <c r="E43" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>SYNHOST00037</v>
+        <v>TUN3x05</v>
       </c>
       <c r="B44" t="str">
         <v>C</v>
@@ -1084,12 +1144,12 @@
         <v>338944</v>
       </c>
       <c r="E44" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>SYNHOST00038</v>
+        <v>NBO3x05</v>
       </c>
       <c r="B45" t="str">
         <v>C</v>
@@ -1101,12 +1161,12 @@
         <v>358400</v>
       </c>
       <c r="E45" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>SYNHOST00039</v>
+        <v>JNB3x05</v>
       </c>
       <c r="B46" t="str">
         <v>C</v>
@@ -1118,12 +1178,12 @@
         <v>470016</v>
       </c>
       <c r="E46" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>SYNHOST00040</v>
+        <v>PEK3x05</v>
       </c>
       <c r="B47" t="str">
         <v>C</v>
@@ -1135,12 +1195,12 @@
         <v>318464</v>
       </c>
       <c r="E47" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>SYNHOST00041</v>
+        <v>PVG3x05</v>
       </c>
       <c r="B48" t="str">
         <v>C</v>
@@ -1152,12 +1212,12 @@
         <v>223232</v>
       </c>
       <c r="E48" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>SYNHOST00042</v>
+        <v>ICN3x05</v>
       </c>
       <c r="B49" t="str">
         <v>C</v>
@@ -1169,12 +1229,12 @@
         <v>442368</v>
       </c>
       <c r="E49" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>SYNHOST00043</v>
+        <v>NRT3x05</v>
       </c>
       <c r="B50" t="str">
         <v>C</v>
@@ -1186,12 +1246,12 @@
         <v>227328</v>
       </c>
       <c r="E50" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>SYNHOST00044</v>
+        <v>SIN3x05</v>
       </c>
       <c r="B51" t="str">
         <v>C</v>
@@ -1203,12 +1263,12 @@
         <v>357376</v>
       </c>
       <c r="E51" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>SYNHOST00045</v>
+        <v>BKK3x05</v>
       </c>
       <c r="B52" t="str">
         <v>C</v>
@@ -1220,12 +1280,12 @@
         <v>365568</v>
       </c>
       <c r="E52" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>SYNHOST00046</v>
+        <v>DEL3x05</v>
       </c>
       <c r="B53" t="str">
         <v>C</v>
@@ -1237,12 +1297,12 @@
         <v>275456</v>
       </c>
       <c r="E53" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>SYNHOST00047</v>
+        <v>BOM3x05</v>
       </c>
       <c r="B54" t="str">
         <v>C</v>
@@ -1254,12 +1314,12 @@
         <v>210944</v>
       </c>
       <c r="E54" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>SYNHOST00048</v>
+        <v>IST0x18</v>
       </c>
       <c r="B55" t="str">
         <v>C</v>
@@ -1271,12 +1331,12 @@
         <v>429056</v>
       </c>
       <c r="E55" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>SYNHOST00049</v>
+        <v>SAW0x18</v>
       </c>
       <c r="B56" t="str">
         <v>C</v>
@@ -1288,12 +1348,12 @@
         <v>475136</v>
       </c>
       <c r="E56" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>SYNHOST00050</v>
+        <v>ESB0x18</v>
       </c>
       <c r="B57" t="str">
         <v>C</v>
@@ -1305,12 +1365,12 @@
         <v>310272</v>
       </c>
       <c r="E57" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>SYNHOST00051</v>
+        <v>ADB0x18</v>
       </c>
       <c r="B58" t="str">
         <v>C</v>
@@ -1322,12 +1382,12 @@
         <v>345088</v>
       </c>
       <c r="E58" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>SYNHOST00052</v>
+        <v>AYT0x18</v>
       </c>
       <c r="B59" t="str">
         <v>C</v>
@@ -1339,12 +1399,12 @@
         <v>337920</v>
       </c>
       <c r="E59" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>SYNHOST00053</v>
+        <v>ADA0x18</v>
       </c>
       <c r="B60" t="str">
         <v>C</v>
@@ -1356,12 +1416,12 @@
         <v>361472</v>
       </c>
       <c r="E60" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>SYNHOST00054</v>
+        <v>TZX0x18</v>
       </c>
       <c r="B61" t="str">
         <v>C</v>
@@ -1373,12 +1433,12 @@
         <v>315392</v>
       </c>
       <c r="E61" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>SYNHOST00055</v>
+        <v>GZT0x18</v>
       </c>
       <c r="B62" t="str">
         <v>C</v>
@@ -1390,12 +1450,12 @@
         <v>311296</v>
       </c>
       <c r="E62" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>SYNHOST00056</v>
+        <v>KYA0x18</v>
       </c>
       <c r="B63" t="str">
         <v>C</v>
@@ -1407,12 +1467,12 @@
         <v>417792</v>
       </c>
       <c r="E63" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>SYNHOST00057</v>
+        <v>VAN0x18</v>
       </c>
       <c r="B64" t="str">
         <v>C</v>
@@ -1424,12 +1484,12 @@
         <v>217088</v>
       </c>
       <c r="E64" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>SYNHOST00058</v>
+        <v>JFK0x18</v>
       </c>
       <c r="B65" t="str">
         <v>C</v>
@@ -1441,12 +1501,12 @@
         <v>501760</v>
       </c>
       <c r="E65" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>SYNHOST00059</v>
+        <v>ORD0x18</v>
       </c>
       <c r="B66" t="str">
         <v>C</v>
@@ -1458,12 +1518,12 @@
         <v>356352</v>
       </c>
       <c r="E66" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>SYNHOST00060</v>
+        <v>IAD0x18</v>
       </c>
       <c r="B67" t="str">
         <v>C</v>
@@ -1475,12 +1535,12 @@
         <v>281600</v>
       </c>
       <c r="E67" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>SYNHOST00061</v>
+        <v>LAX0x18</v>
       </c>
       <c r="B68" t="str">
         <v>C</v>
@@ -1492,12 +1552,12 @@
         <v>289792</v>
       </c>
       <c r="E68" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>SYNHOST00062</v>
+        <v>MIA0x18</v>
       </c>
       <c r="B69" t="str">
         <v>C</v>
@@ -1509,12 +1569,12 @@
         <v>365568</v>
       </c>
       <c r="E69" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>SYNHOST00063</v>
+        <v>BOS0x18</v>
       </c>
       <c r="B70" t="str">
         <v>C</v>
@@ -1526,12 +1586,12 @@
         <v>239616</v>
       </c>
       <c r="E70" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>SYNHOST00064</v>
+        <v>LHR0x18</v>
       </c>
       <c r="B71" t="str">
         <v>C</v>
@@ -1543,12 +1603,12 @@
         <v>407552</v>
       </c>
       <c r="E71" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>SYNHOST00065</v>
+        <v>CDG0x18</v>
       </c>
       <c r="B72" t="str">
         <v>C</v>
@@ -1560,12 +1620,12 @@
         <v>328704</v>
       </c>
       <c r="E72" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>SYNHOST00066</v>
+        <v>FRA0x18</v>
       </c>
       <c r="B73" t="str">
         <v>C</v>
@@ -1577,12 +1637,12 @@
         <v>506880</v>
       </c>
       <c r="E73" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>SYNHOST00067</v>
+        <v>AMS0x18</v>
       </c>
       <c r="B74" t="str">
         <v>C</v>
@@ -1594,12 +1654,12 @@
         <v>297984</v>
       </c>
       <c r="E74" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>SYNHOST00068</v>
+        <v>MAD0x18</v>
       </c>
       <c r="B75" t="str">
         <v>C</v>
@@ -1611,12 +1671,12 @@
         <v>230400</v>
       </c>
       <c r="E75" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>SYNHOST00069</v>
+        <v>FCO0x18</v>
       </c>
       <c r="B76" t="str">
         <v>C</v>
@@ -1628,12 +1688,12 @@
         <v>398336</v>
       </c>
       <c r="E76" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>SYNHOST00070</v>
+        <v>MUC0x18</v>
       </c>
       <c r="B77" t="str">
         <v>C</v>
@@ -1645,12 +1705,12 @@
         <v>494592</v>
       </c>
       <c r="E77" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>SYNHOST00071</v>
+        <v>ZRH0x18</v>
       </c>
       <c r="B78" t="str">
         <v>C</v>
@@ -1662,12 +1722,12 @@
         <v>351232</v>
       </c>
       <c r="E78" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>SYNHOST00072</v>
+        <v>VIE0x18</v>
       </c>
       <c r="B79" t="str">
         <v>C</v>
@@ -1679,12 +1739,12 @@
         <v>218112</v>
       </c>
       <c r="E79" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>SYNHOST00073</v>
+        <v>BRU0x18</v>
       </c>
       <c r="B80" t="str">
         <v>C</v>
@@ -1696,12 +1756,12 @@
         <v>437248</v>
       </c>
       <c r="E80" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>SYNHOST00074</v>
+        <v>CPH0x18</v>
       </c>
       <c r="B81" t="str">
         <v>C</v>
@@ -1713,12 +1773,12 @@
         <v>486400</v>
       </c>
       <c r="E81" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>SYNHOST00075</v>
+        <v>ARN0x18</v>
       </c>
       <c r="B82" t="str">
         <v>C</v>
@@ -1730,12 +1790,12 @@
         <v>231424</v>
       </c>
       <c r="E82" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>SYNHOST00076</v>
+        <v>OSL0x18</v>
       </c>
       <c r="B83" t="str">
         <v>C</v>
@@ -1747,12 +1807,12 @@
         <v>375808</v>
       </c>
       <c r="E83" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>SYNHOST00077</v>
+        <v>WAW0x18</v>
       </c>
       <c r="B84" t="str">
         <v>C</v>
@@ -1764,12 +1824,12 @@
         <v>453632</v>
       </c>
       <c r="E84" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>SYNHOST00078</v>
+        <v>PRG0x18</v>
       </c>
       <c r="B85" t="str">
         <v>C</v>
@@ -1781,12 +1841,12 @@
         <v>467968</v>
       </c>
       <c r="E85" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>SYNHOST00079</v>
+        <v>BUD0x18</v>
       </c>
       <c r="B86" t="str">
         <v>C</v>
@@ -1798,12 +1858,12 @@
         <v>235520</v>
       </c>
       <c r="E86" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>SYNHOST00080</v>
+        <v>DXB0x18</v>
       </c>
       <c r="B87" t="str">
         <v>C</v>
@@ -1815,12 +1875,12 @@
         <v>300032</v>
       </c>
       <c r="E87" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>SYNHOST00081</v>
+        <v>DOH0x18</v>
       </c>
       <c r="B88" t="str">
         <v>C</v>
@@ -1832,12 +1892,12 @@
         <v>342016</v>
       </c>
       <c r="E88" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>SYNHOST00082</v>
+        <v>JED0x18</v>
       </c>
       <c r="B89" t="str">
         <v>C</v>
@@ -1849,12 +1909,12 @@
         <v>296960</v>
       </c>
       <c r="E89" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>SYNHOST00083</v>
+        <v>CAI0x18</v>
       </c>
       <c r="B90" t="str">
         <v>C</v>
@@ -1866,12 +1926,12 @@
         <v>344064</v>
       </c>
       <c r="E90" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>SYNHOST00084</v>
+        <v>ALG0x18</v>
       </c>
       <c r="B91" t="str">
         <v>C</v>
@@ -1883,12 +1943,12 @@
         <v>496640</v>
       </c>
       <c r="E91" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>SYNHOST00085</v>
+        <v>TUN0x18</v>
       </c>
       <c r="B92" t="str">
         <v>C</v>
@@ -1900,12 +1960,12 @@
         <v>325632</v>
       </c>
       <c r="E92" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>SYNHOST00086</v>
+        <v>NBO0x18</v>
       </c>
       <c r="B93" t="str">
         <v>C</v>
@@ -1917,12 +1977,12 @@
         <v>329728</v>
       </c>
       <c r="E93" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>SYNHOST00087</v>
+        <v>JNB0x18</v>
       </c>
       <c r="B94" t="str">
         <v>C</v>
@@ -1934,12 +1994,12 @@
         <v>491520</v>
       </c>
       <c r="E94" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>SYNHOST00088</v>
+        <v>PEK0x18</v>
       </c>
       <c r="B95" t="str">
         <v>C</v>
@@ -1951,12 +2011,12 @@
         <v>343040</v>
       </c>
       <c r="E95" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>SYNHOST00089</v>
+        <v>PVG0x18</v>
       </c>
       <c r="B96" t="str">
         <v>C</v>
@@ -1968,12 +2028,12 @@
         <v>449536</v>
       </c>
       <c r="E96" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>SYNHOST00090</v>
+        <v>ICN0x18</v>
       </c>
       <c r="B97" t="str">
         <v>C</v>
@@ -1985,12 +2045,12 @@
         <v>449536</v>
       </c>
       <c r="E97" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>SYNHOST00091</v>
+        <v>NRT0x18</v>
       </c>
       <c r="B98" t="str">
         <v>C</v>
@@ -2002,12 +2062,12 @@
         <v>337920</v>
       </c>
       <c r="E98" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>SYNHOST00092</v>
+        <v>SIN0x18</v>
       </c>
       <c r="B99" t="str">
         <v>C</v>
@@ -2019,12 +2079,12 @@
         <v>256000</v>
       </c>
       <c r="E99" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>SYNHOST00093</v>
+        <v>BKK0x18</v>
       </c>
       <c r="B100" t="str">
         <v>C</v>
@@ -2036,12 +2096,12 @@
         <v>324608</v>
       </c>
       <c r="E100" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>SYNHOST00094</v>
+        <v>DEL0x18</v>
       </c>
       <c r="B101" t="str">
         <v>C</v>
@@ -2053,12 +2113,12 @@
         <v>271360</v>
       </c>
       <c r="E101" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>SYNHOST00095</v>
+        <v>BOM0x18</v>
       </c>
       <c r="B102" t="str">
         <v>C</v>
@@ -2070,12 +2130,12 @@
         <v>296960</v>
       </c>
       <c r="E102" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>SYNHOST00096</v>
+        <v>IST7x31</v>
       </c>
       <c r="B103" t="str">
         <v>C</v>
@@ -2087,12 +2147,12 @@
         <v>316416</v>
       </c>
       <c r="E103" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>SYNHOST00097</v>
+        <v>SAW7x31</v>
       </c>
       <c r="B104" t="str">
         <v>C</v>
@@ -2104,12 +2164,12 @@
         <v>253952</v>
       </c>
       <c r="E104" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>SYNHOST00098</v>
+        <v>ESB7x31</v>
       </c>
       <c r="B105" t="str">
         <v>C</v>
@@ -2121,12 +2181,12 @@
         <v>424960</v>
       </c>
       <c r="E105" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>SYNHOST00099</v>
+        <v>ADB7x31</v>
       </c>
       <c r="B106" t="str">
         <v>C</v>
@@ -2138,12 +2198,12 @@
         <v>467968</v>
       </c>
       <c r="E106" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>SYNHOST00100</v>
+        <v>AYT7x31</v>
       </c>
       <c r="B107" t="str">
         <v>C</v>
@@ -2155,12 +2215,12 @@
         <v>339968</v>
       </c>
       <c r="E107" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>SYNHOST00101</v>
+        <v>ADA7x31</v>
       </c>
       <c r="B108" t="str">
         <v>C</v>
@@ -2172,12 +2232,12 @@
         <v>348160</v>
       </c>
       <c r="E108" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>SYNHOST00102</v>
+        <v>TZX7x31</v>
       </c>
       <c r="B109" t="str">
         <v>C</v>
@@ -2189,12 +2249,12 @@
         <v>233472</v>
       </c>
       <c r="E109" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>SYNHOST00103</v>
+        <v>GZT7x31</v>
       </c>
       <c r="B110" t="str">
         <v>C</v>
@@ -2206,12 +2266,12 @@
         <v>292864</v>
       </c>
       <c r="E110" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>SYNHOST00104</v>
+        <v>KYA7x31</v>
       </c>
       <c r="B111" t="str">
         <v>C</v>
@@ -2223,12 +2283,12 @@
         <v>272384</v>
       </c>
       <c r="E111" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>SYNHOST00105</v>
+        <v>VAN7x31</v>
       </c>
       <c r="B112" t="str">
         <v>C</v>
@@ -2240,12 +2300,12 @@
         <v>283648</v>
       </c>
       <c r="E112" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>SYNHOST00106</v>
+        <v>JFK7x31</v>
       </c>
       <c r="B113" t="str">
         <v>C</v>
@@ -2257,12 +2317,12 @@
         <v>269312</v>
       </c>
       <c r="E113" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>SYNHOST00107</v>
+        <v>ORD7x31</v>
       </c>
       <c r="B114" t="str">
         <v>C</v>
@@ -2274,12 +2334,12 @@
         <v>220160</v>
       </c>
       <c r="E114" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>SYNHOST00108</v>
+        <v>IAD7x31</v>
       </c>
       <c r="B115" t="str">
         <v>C</v>
@@ -2291,12 +2351,12 @@
         <v>209920</v>
       </c>
       <c r="E115" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>SYNHOST00109</v>
+        <v>LAX7x31</v>
       </c>
       <c r="B116" t="str">
         <v>C</v>
@@ -2308,12 +2368,12 @@
         <v>379904</v>
       </c>
       <c r="E116" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>SYNHOST00110</v>
+        <v>MIA7x31</v>
       </c>
       <c r="B117" t="str">
         <v>C</v>
@@ -2325,12 +2385,12 @@
         <v>400384</v>
       </c>
       <c r="E117" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>SYNHOST00111</v>
+        <v>BOS7x31</v>
       </c>
       <c r="B118" t="str">
         <v>C</v>
@@ -2342,12 +2402,12 @@
         <v>484352</v>
       </c>
       <c r="E118" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>SYNHOST00112</v>
+        <v>LHR7x31</v>
       </c>
       <c r="B119" t="str">
         <v>C</v>
@@ -2359,12 +2419,12 @@
         <v>377856</v>
       </c>
       <c r="E119" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>SYNHOST00113</v>
+        <v>CDG7x31</v>
       </c>
       <c r="B120" t="str">
         <v>C</v>
@@ -2376,12 +2436,12 @@
         <v>343040</v>
       </c>
       <c r="E120" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>SYNHOST00114</v>
+        <v>FRA7x31</v>
       </c>
       <c r="B121" t="str">
         <v>C</v>
@@ -2393,12 +2453,12 @@
         <v>353280</v>
       </c>
       <c r="E121" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>SYNHOST00115</v>
+        <v>AMS7x31</v>
       </c>
       <c r="B122" t="str">
         <v>C</v>
@@ -2410,12 +2470,12 @@
         <v>337920</v>
       </c>
       <c r="E122" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>SYNHOST00116</v>
+        <v>MAD7x31</v>
       </c>
       <c r="B123" t="str">
         <v>C</v>
@@ -2427,12 +2487,12 @@
         <v>399360</v>
       </c>
       <c r="E123" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>SYNHOST00117</v>
+        <v>FCO7x31</v>
       </c>
       <c r="B124" t="str">
         <v>C</v>
@@ -2444,12 +2504,12 @@
         <v>395264</v>
       </c>
       <c r="E124" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>SYNHOST00118</v>
+        <v>MUC7x31</v>
       </c>
       <c r="B125" t="str">
         <v>C</v>
@@ -2461,12 +2521,12 @@
         <v>457728</v>
       </c>
       <c r="E125" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>SYNHOST00119</v>
+        <v>ZRH7x31</v>
       </c>
       <c r="B126" t="str">
         <v>C</v>
@@ -2478,12 +2538,12 @@
         <v>445440</v>
       </c>
       <c r="E126" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>SYNHOST00120</v>
+        <v>VIE7x31</v>
       </c>
       <c r="B127" t="str">
         <v>C</v>
@@ -2495,12 +2555,12 @@
         <v>379904</v>
       </c>
       <c r="E127" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>SYNHOST00121</v>
+        <v>BRU7x31</v>
       </c>
       <c r="B128" t="str">
         <v>C</v>
@@ -2512,12 +2572,12 @@
         <v>310272</v>
       </c>
       <c r="E128" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>SYNHOST00122</v>
+        <v>CPH7x31</v>
       </c>
       <c r="B129" t="str">
         <v>C</v>
@@ -2529,12 +2589,12 @@
         <v>274432</v>
       </c>
       <c r="E129" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>SYNHOST00123</v>
+        <v>ARN7x31</v>
       </c>
       <c r="B130" t="str">
         <v>C</v>
@@ -2546,12 +2606,12 @@
         <v>505856</v>
       </c>
       <c r="E130" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>SYNHOST00124</v>
+        <v>OSL7x31</v>
       </c>
       <c r="B131" t="str">
         <v>C</v>
@@ -2563,12 +2623,12 @@
         <v>503808</v>
       </c>
       <c r="E131" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>SYNHOST00125</v>
+        <v>WAW7x31</v>
       </c>
       <c r="B132" t="str">
         <v>C</v>
@@ -2580,12 +2640,12 @@
         <v>279552</v>
       </c>
       <c r="E132" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>SYNHOST00126</v>
+        <v>PRG7x31</v>
       </c>
       <c r="B133" t="str">
         <v>C</v>
@@ -2597,12 +2657,12 @@
         <v>427008</v>
       </c>
       <c r="E133" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>SYNHOST00127</v>
+        <v>BUD7x31</v>
       </c>
       <c r="B134" t="str">
         <v>C</v>
@@ -2614,12 +2674,12 @@
         <v>215040</v>
       </c>
       <c r="E134" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>SYNHOST00128</v>
+        <v>DXB7x31</v>
       </c>
       <c r="B135" t="str">
         <v>C</v>
@@ -2631,12 +2691,12 @@
         <v>506880</v>
       </c>
       <c r="E135" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>SYNHOST00129</v>
+        <v>DOH7x31</v>
       </c>
       <c r="B136" t="str">
         <v>C</v>
@@ -2648,12 +2708,12 @@
         <v>368640</v>
       </c>
       <c r="E136" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>SYNHOST00130</v>
+        <v>JED7x31</v>
       </c>
       <c r="B137" t="str">
         <v>C</v>
@@ -2665,12 +2725,12 @@
         <v>259072</v>
       </c>
       <c r="E137" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>SYNHOST00131</v>
+        <v>CAI7x31</v>
       </c>
       <c r="B138" t="str">
         <v>C</v>
@@ -2682,12 +2742,12 @@
         <v>253952</v>
       </c>
       <c r="E138" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>SYNHOST00132</v>
+        <v>ALG7x31</v>
       </c>
       <c r="B139" t="str">
         <v>C</v>
@@ -2699,12 +2759,12 @@
         <v>305152</v>
       </c>
       <c r="E139" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>SYNHOST00133</v>
+        <v>TUN7x31</v>
       </c>
       <c r="B140" t="str">
         <v>C</v>
@@ -2716,12 +2776,12 @@
         <v>230400</v>
       </c>
       <c r="E140" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>SYNHOST00134</v>
+        <v>NBO7x31</v>
       </c>
       <c r="B141" t="str">
         <v>C</v>
@@ -2733,12 +2793,12 @@
         <v>328704</v>
       </c>
       <c r="E141" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>SYNHOST00135</v>
+        <v>JNB7x31</v>
       </c>
       <c r="B142" t="str">
         <v>C</v>
@@ -2750,12 +2810,12 @@
         <v>342016</v>
       </c>
       <c r="E142" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>SYNHOST00136</v>
+        <v>PEK7x31</v>
       </c>
       <c r="B143" t="str">
         <v>C</v>
@@ -2767,12 +2827,12 @@
         <v>397312</v>
       </c>
       <c r="E143" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>SYNHOST00137</v>
+        <v>PVG7x31</v>
       </c>
       <c r="B144" t="str">
         <v>C</v>
@@ -2784,12 +2844,12 @@
         <v>209920</v>
       </c>
       <c r="E144" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>SYNHOST00138</v>
+        <v>ICN7x31</v>
       </c>
       <c r="B145" t="str">
         <v>C</v>
@@ -2801,12 +2861,12 @@
         <v>323584</v>
       </c>
       <c r="E145" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>SYNHOST00139</v>
+        <v>NRT7x31</v>
       </c>
       <c r="B146" t="str">
         <v>C</v>
@@ -2818,12 +2878,12 @@
         <v>355328</v>
       </c>
       <c r="E146" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>SYNHOST00140</v>
+        <v>SIN7x31</v>
       </c>
       <c r="B147" t="str">
         <v>C</v>
@@ -2835,12 +2895,12 @@
         <v>331776</v>
       </c>
       <c r="E147" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>SYNHOST00141</v>
+        <v>BKK7x31</v>
       </c>
       <c r="B148" t="str">
         <v>C</v>
@@ -2852,12 +2912,12 @@
         <v>224256</v>
       </c>
       <c r="E148" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>SYNHOST00142</v>
+        <v>DEL7x31</v>
       </c>
       <c r="B149" t="str">
         <v>C</v>
@@ -2869,12 +2929,12 @@
         <v>252928</v>
       </c>
       <c r="E149" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>SYNHOST00143</v>
+        <v>BOM7x31</v>
       </c>
       <c r="B150" t="str">
         <v>C</v>
@@ -2886,12 +2946,12 @@
         <v>300032</v>
       </c>
       <c r="E150" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>SYNHOST00144</v>
+        <v>IST4x44</v>
       </c>
       <c r="B151" t="str">
         <v>C</v>
@@ -2903,12 +2963,12 @@
         <v>266240</v>
       </c>
       <c r="E151" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>SYNHOST00145</v>
+        <v>SAW4x44</v>
       </c>
       <c r="B152" t="str">
         <v>C</v>
@@ -2920,12 +2980,12 @@
         <v>257024</v>
       </c>
       <c r="E152" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>SYNHOST00146</v>
+        <v>ESB4x44</v>
       </c>
       <c r="B153" t="str">
         <v>C</v>
@@ -2937,12 +2997,12 @@
         <v>496640</v>
       </c>
       <c r="E153" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>SYNHOST00147</v>
+        <v>ADB4x44</v>
       </c>
       <c r="B154" t="str">
         <v>C</v>
@@ -2954,12 +3014,12 @@
         <v>375808</v>
       </c>
       <c r="E154" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>SYNHOST00148</v>
+        <v>AYT4x44</v>
       </c>
       <c r="B155" t="str">
         <v>C</v>
@@ -2971,12 +3031,12 @@
         <v>430080</v>
       </c>
       <c r="E155" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>SYNHOST00149</v>
+        <v>ADA4x44</v>
       </c>
       <c r="B156" t="str">
         <v>C</v>
@@ -2988,12 +3048,12 @@
         <v>465920</v>
       </c>
       <c r="E156" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>SYNHOST00150</v>
+        <v>TZX4x44</v>
       </c>
       <c r="B157" t="str">
         <v>C</v>
@@ -3005,12 +3065,12 @@
         <v>412672</v>
       </c>
       <c r="E157" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>SYNHOST00151</v>
+        <v>GZT4x44</v>
       </c>
       <c r="B158" t="str">
         <v>C</v>
@@ -3022,12 +3082,12 @@
         <v>506880</v>
       </c>
       <c r="E158" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>SYNHOST00152</v>
+        <v>KYA4x44</v>
       </c>
       <c r="B159" t="str">
         <v>C</v>
@@ -3039,12 +3099,12 @@
         <v>289792</v>
       </c>
       <c r="E159" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>SYNHOST00153</v>
+        <v>VAN4x44</v>
       </c>
       <c r="B160" t="str">
         <v>C</v>
@@ -3056,12 +3116,12 @@
         <v>453632</v>
       </c>
       <c r="E160" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>SYNHOST00154</v>
+        <v>JFK4x44</v>
       </c>
       <c r="B161" t="str">
         <v>C</v>
@@ -3073,12 +3133,12 @@
         <v>362496</v>
       </c>
       <c r="E161" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>SYNHOST00155</v>
+        <v>ORD4x44</v>
       </c>
       <c r="B162" t="str">
         <v>C</v>
@@ -3090,12 +3150,12 @@
         <v>364544</v>
       </c>
       <c r="E162" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>SYNHOST00156</v>
+        <v>IAD4x44</v>
       </c>
       <c r="B163" t="str">
         <v>C</v>
@@ -3107,12 +3167,12 @@
         <v>449536</v>
       </c>
       <c r="E163" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>SYNHOST00157</v>
+        <v>LAX4x44</v>
       </c>
       <c r="B164" t="str">
         <v>C</v>
@@ -3124,12 +3184,12 @@
         <v>322560</v>
       </c>
       <c r="E164" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>SYNHOST00158</v>
+        <v>MIA4x44</v>
       </c>
       <c r="B165" t="str">
         <v>C</v>
@@ -3141,12 +3201,12 @@
         <v>473088</v>
       </c>
       <c r="E165" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>SYNHOST00159</v>
+        <v>BOS4x44</v>
       </c>
       <c r="B166" t="str">
         <v>C</v>
@@ -3158,12 +3218,12 @@
         <v>415744</v>
       </c>
       <c r="E166" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>SYNHOST00160</v>
+        <v>LHR4x44</v>
       </c>
       <c r="B167" t="str">
         <v>C</v>
@@ -3175,12 +3235,12 @@
         <v>254976</v>
       </c>
       <c r="E167" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>SYNHOST00161</v>
+        <v>CDG4x44</v>
       </c>
       <c r="B168" t="str">
         <v>C</v>
@@ -3192,12 +3252,12 @@
         <v>308224</v>
       </c>
       <c r="E168" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>SYNHOST00162</v>
+        <v>FRA4x44</v>
       </c>
       <c r="B169" t="str">
         <v>C</v>
@@ -3209,12 +3269,12 @@
         <v>486400</v>
       </c>
       <c r="E169" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>SYNHOST00163</v>
+        <v>AMS4x44</v>
       </c>
       <c r="B170" t="str">
         <v>C</v>
@@ -3226,12 +3286,12 @@
         <v>239616</v>
       </c>
       <c r="E170" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>SYNHOST00164</v>
+        <v>MAD4x44</v>
       </c>
       <c r="B171" t="str">
         <v>C</v>
@@ -3243,12 +3303,12 @@
         <v>332800</v>
       </c>
       <c r="E171" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>SYNHOST00165</v>
+        <v>FCO4x44</v>
       </c>
       <c r="B172" t="str">
         <v>C</v>
@@ -3260,12 +3320,12 @@
         <v>402432</v>
       </c>
       <c r="E172" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>SYNHOST00166</v>
+        <v>MUC4x44</v>
       </c>
       <c r="B173" t="str">
         <v>C</v>
@@ -3277,12 +3337,12 @@
         <v>234496</v>
       </c>
       <c r="E173" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>SYNHOST00167</v>
+        <v>ZRH4x44</v>
       </c>
       <c r="B174" t="str">
         <v>C</v>
@@ -3294,12 +3354,12 @@
         <v>258048</v>
       </c>
       <c r="E174" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>SYNHOST00168</v>
+        <v>VIE4x44</v>
       </c>
       <c r="B175" t="str">
         <v>C</v>
@@ -3311,12 +3371,12 @@
         <v>265216</v>
       </c>
       <c r="E175" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>SYNHOST00169</v>
+        <v>BRU4x44</v>
       </c>
       <c r="B176" t="str">
         <v>C</v>
@@ -3328,12 +3388,12 @@
         <v>293888</v>
       </c>
       <c r="E176" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>SYNHOST00170</v>
+        <v>CPH4x44</v>
       </c>
       <c r="B177" t="str">
         <v>C</v>
@@ -3345,12 +3405,12 @@
         <v>278528</v>
       </c>
       <c r="E177" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>SYNHOST00171</v>
+        <v>ARN4x44</v>
       </c>
       <c r="B178" t="str">
         <v>C</v>
@@ -3362,12 +3422,12 @@
         <v>366592</v>
       </c>
       <c r="E178" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>SYNHOST00172</v>
+        <v>OSL4x44</v>
       </c>
       <c r="B179" t="str">
         <v>C</v>
@@ -3379,12 +3439,12 @@
         <v>388096</v>
       </c>
       <c r="E179" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>SYNHOST00173</v>
+        <v>WAW4x44</v>
       </c>
       <c r="B180" t="str">
         <v>C</v>
@@ -3396,12 +3456,12 @@
         <v>220160</v>
       </c>
       <c r="E180" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>SYNHOST00174</v>
+        <v>PRG4x44</v>
       </c>
       <c r="B181" t="str">
         <v>C</v>
@@ -3413,12 +3473,12 @@
         <v>232448</v>
       </c>
       <c r="E181" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>SYNHOST00175</v>
+        <v>BUD4x44</v>
       </c>
       <c r="B182" t="str">
         <v>C</v>
@@ -3430,12 +3490,12 @@
         <v>230400</v>
       </c>
       <c r="E182" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>SYNHOST00176</v>
+        <v>DXB4x44</v>
       </c>
       <c r="B183" t="str">
         <v>C</v>
@@ -3447,12 +3507,12 @@
         <v>501760</v>
       </c>
       <c r="E183" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>SYNHOST00177</v>
+        <v>DOH4x44</v>
       </c>
       <c r="B184" t="str">
         <v>C</v>
@@ -3464,12 +3524,12 @@
         <v>342016</v>
       </c>
       <c r="E184" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>SYNHOST00178</v>
+        <v>JED4x44</v>
       </c>
       <c r="B185" t="str">
         <v>C</v>
@@ -3481,12 +3541,12 @@
         <v>220160</v>
       </c>
       <c r="E185" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>SYNHOST00179</v>
+        <v>CAI4x44</v>
       </c>
       <c r="B186" t="str">
         <v>C</v>
@@ -3498,12 +3558,12 @@
         <v>468992</v>
       </c>
       <c r="E186" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>SYNHOST00180</v>
+        <v>ALG4x44</v>
       </c>
       <c r="B187" t="str">
         <v>C</v>
@@ -3515,12 +3575,12 @@
         <v>412672</v>
       </c>
       <c r="E187" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>SYNHOST00181</v>
+        <v>TUN4x44</v>
       </c>
       <c r="B188" t="str">
         <v>C</v>
@@ -3532,12 +3592,12 @@
         <v>266240</v>
       </c>
       <c r="E188" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>SYNHOST00182</v>
+        <v>NBO4x44</v>
       </c>
       <c r="B189" t="str">
         <v>C</v>
@@ -3549,12 +3609,12 @@
         <v>395264</v>
       </c>
       <c r="E189" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>SYNHOST00183</v>
+        <v>JNB4x44</v>
       </c>
       <c r="B190" t="str">
         <v>C</v>
@@ -3566,12 +3626,12 @@
         <v>324608</v>
       </c>
       <c r="E190" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>SYNHOST00184</v>
+        <v>PEK4x44</v>
       </c>
       <c r="B191" t="str">
         <v>C</v>
@@ -3583,12 +3643,12 @@
         <v>256000</v>
       </c>
       <c r="E191" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>SYNHOST00185</v>
+        <v>PVG4x44</v>
       </c>
       <c r="B192" t="str">
         <v>C</v>
@@ -3600,12 +3660,12 @@
         <v>267264</v>
       </c>
       <c r="E192" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>SYNHOST00186</v>
+        <v>ICN4x44</v>
       </c>
       <c r="B193" t="str">
         <v>C</v>
@@ -3617,12 +3677,12 @@
         <v>272384</v>
       </c>
       <c r="E193" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>SYNHOST00187</v>
+        <v>NRT4x44</v>
       </c>
       <c r="B194" t="str">
         <v>C</v>
@@ -3634,12 +3694,12 @@
         <v>229376</v>
       </c>
       <c r="E194" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>SYNHOST00188</v>
+        <v>SIN4x44</v>
       </c>
       <c r="B195" t="str">
         <v>C</v>
@@ -3651,12 +3711,12 @@
         <v>381952</v>
       </c>
       <c r="E195" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>SYNHOST00189</v>
+        <v>BKK4x44</v>
       </c>
       <c r="B196" t="str">
         <v>C</v>
@@ -3668,12 +3728,12 @@
         <v>266240</v>
       </c>
       <c r="E196" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>SYNHOST00190</v>
+        <v>DEL4x44</v>
       </c>
       <c r="B197" t="str">
         <v>C</v>
@@ -3685,12 +3745,12 @@
         <v>462848</v>
       </c>
       <c r="E197" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>SYNHOST00191</v>
+        <v>BOM4x44</v>
       </c>
       <c r="B198" t="str">
         <v>C</v>
@@ -3702,12 +3762,12 @@
         <v>234496</v>
       </c>
       <c r="E198" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>SYNHOST00192</v>
+        <v>IST1x57</v>
       </c>
       <c r="B199" t="str">
         <v>C</v>
@@ -3719,12 +3779,12 @@
         <v>350208</v>
       </c>
       <c r="E199" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>SYNHOST00193</v>
+        <v>SAW1x57</v>
       </c>
       <c r="B200" t="str">
         <v>C</v>
@@ -3736,12 +3796,12 @@
         <v>319488</v>
       </c>
       <c r="E200" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>SYNHOST00194</v>
+        <v>ESB1x57</v>
       </c>
       <c r="B201" t="str">
         <v>C</v>
@@ -3753,12 +3813,12 @@
         <v>205824</v>
       </c>
       <c r="E201" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>SYNHOST00195</v>
+        <v>ADB1x57</v>
       </c>
       <c r="B202" t="str">
         <v>C</v>
@@ -3770,12 +3830,12 @@
         <v>245760</v>
       </c>
       <c r="E202" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>SYNHOST00196</v>
+        <v>AYT1x57</v>
       </c>
       <c r="B203" t="str">
         <v>C</v>
@@ -3787,12 +3847,12 @@
         <v>460800</v>
       </c>
       <c r="E203" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>SYNHOST00197</v>
+        <v>ADA1x57</v>
       </c>
       <c r="B204" t="str">
         <v>C</v>
@@ -3804,12 +3864,12 @@
         <v>277504</v>
       </c>
       <c r="E204" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>SYNHOST00198</v>
+        <v>TZX1x57</v>
       </c>
       <c r="B205" t="str">
         <v>C</v>
@@ -3821,12 +3881,12 @@
         <v>252928</v>
       </c>
       <c r="E205" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>SYNHOST00199</v>
+        <v>GZT1x57</v>
       </c>
       <c r="B206" t="str">
         <v>C</v>
@@ -3838,12 +3898,12 @@
         <v>376832</v>
       </c>
       <c r="E206" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>SYNHOST00200</v>
+        <v>KYA1x57</v>
       </c>
       <c r="B207" t="str">
         <v>C</v>
@@ -3855,12 +3915,12 @@
         <v>289792</v>
       </c>
       <c r="E207" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>SYNHOST00201</v>
+        <v>VAN1x57</v>
       </c>
       <c r="B208" t="str">
         <v>C</v>
@@ -3872,12 +3932,12 @@
         <v>354304</v>
       </c>
       <c r="E208" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>SYNHOST00202</v>
+        <v>JFK1x57</v>
       </c>
       <c r="B209" t="str">
         <v>C</v>
@@ -3889,12 +3949,12 @@
         <v>507904</v>
       </c>
       <c r="E209" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>SYNHOST00203</v>
+        <v>ORD1x57</v>
       </c>
       <c r="B210" t="str">
         <v>C</v>
@@ -3906,12 +3966,12 @@
         <v>379904</v>
       </c>
       <c r="E210" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>SYNHOST00204</v>
+        <v>IAD1x57</v>
       </c>
       <c r="B211" t="str">
         <v>C</v>
@@ -3923,12 +3983,12 @@
         <v>212992</v>
       </c>
       <c r="E211" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>SYNHOST00205</v>
+        <v>LAX1x57</v>
       </c>
       <c r="B212" t="str">
         <v>C</v>
@@ -3940,12 +4000,12 @@
         <v>312320</v>
       </c>
       <c r="E212" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>SYNHOST00206</v>
+        <v>MIA1x57</v>
       </c>
       <c r="B213" t="str">
         <v>C</v>
@@ -3957,12 +4017,12 @@
         <v>300032</v>
       </c>
       <c r="E213" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>SYNHOST00207</v>
+        <v>BOS1x57</v>
       </c>
       <c r="B214" t="str">
         <v>C</v>
@@ -3974,12 +4034,12 @@
         <v>215040</v>
       </c>
       <c r="E214" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>SYNHOST00208</v>
+        <v>LHR1x57</v>
       </c>
       <c r="B215" t="str">
         <v>C</v>
@@ -3991,12 +4051,12 @@
         <v>388096</v>
       </c>
       <c r="E215" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>SYNHOST00209</v>
+        <v>CDG1x57</v>
       </c>
       <c r="B216" t="str">
         <v>C</v>
@@ -4008,12 +4068,12 @@
         <v>312320</v>
       </c>
       <c r="E216" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>SYNHOST00210</v>
+        <v>FRA1x57</v>
       </c>
       <c r="B217" t="str">
         <v>C</v>
@@ -4025,12 +4085,12 @@
         <v>392192</v>
       </c>
       <c r="E217" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>SYNHOST00211</v>
+        <v>AMS1x57</v>
       </c>
       <c r="B218" t="str">
         <v>C</v>
@@ -4042,12 +4102,12 @@
         <v>412672</v>
       </c>
       <c r="E218" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>SYNHOST00212</v>
+        <v>MAD1x57</v>
       </c>
       <c r="B219" t="str">
         <v>C</v>
@@ -4059,12 +4119,12 @@
         <v>235520</v>
       </c>
       <c r="E219" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>SYNHOST00213</v>
+        <v>FCO1x57</v>
       </c>
       <c r="B220" t="str">
         <v>C</v>
@@ -4076,12 +4136,12 @@
         <v>227328</v>
       </c>
       <c r="E220" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>SYNHOST00214</v>
+        <v>MUC1x57</v>
       </c>
       <c r="B221" t="str">
         <v>C</v>
@@ -4093,12 +4153,12 @@
         <v>499712</v>
       </c>
       <c r="E221" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>SYNHOST00215</v>
+        <v>ZRH1x57</v>
       </c>
       <c r="B222" t="str">
         <v>C</v>
@@ -4110,12 +4170,12 @@
         <v>323584</v>
       </c>
       <c r="E222" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>SYNHOST00216</v>
+        <v>VIE1x57</v>
       </c>
       <c r="B223" t="str">
         <v>C</v>
@@ -4127,12 +4187,12 @@
         <v>412672</v>
       </c>
       <c r="E223" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>SYNHOST00217</v>
+        <v>BRU1x57</v>
       </c>
       <c r="B224" t="str">
         <v>C</v>
@@ -4144,12 +4204,12 @@
         <v>470016</v>
       </c>
       <c r="E224" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>SYNHOST00218</v>
+        <v>CPH1x57</v>
       </c>
       <c r="B225" t="str">
         <v>C</v>
@@ -4161,12 +4221,12 @@
         <v>311296</v>
       </c>
       <c r="E225" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>SYNHOST00219</v>
+        <v>ARN1x57</v>
       </c>
       <c r="B226" t="str">
         <v>C</v>
@@ -4178,12 +4238,12 @@
         <v>338944</v>
       </c>
       <c r="E226" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>SYNHOST00220</v>
+        <v>OSL1x57</v>
       </c>
       <c r="B227" t="str">
         <v>C</v>
@@ -4195,12 +4255,12 @@
         <v>252928</v>
       </c>
       <c r="E227" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>SYNHOST00221</v>
+        <v>WAW1x57</v>
       </c>
       <c r="B228" t="str">
         <v>C</v>
@@ -4212,12 +4272,12 @@
         <v>407552</v>
       </c>
       <c r="E228" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>SYNHOST00222</v>
+        <v>PRG1x57</v>
       </c>
       <c r="B229" t="str">
         <v>C</v>
@@ -4229,12 +4289,12 @@
         <v>215040</v>
       </c>
       <c r="E229" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>SYNHOST00223</v>
+        <v>BUD1x57</v>
       </c>
       <c r="B230" t="str">
         <v>C</v>
@@ -4246,12 +4306,12 @@
         <v>326656</v>
       </c>
       <c r="E230" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>SYNHOST00224</v>
+        <v>DXB1x57</v>
       </c>
       <c r="B231" t="str">
         <v>C</v>
@@ -4263,12 +4323,12 @@
         <v>363520</v>
       </c>
       <c r="E231" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>SYNHOST00225</v>
+        <v>DOH1x57</v>
       </c>
       <c r="B232" t="str">
         <v>C</v>
@@ -4280,12 +4340,12 @@
         <v>463872</v>
       </c>
       <c r="E232" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>SYNHOST00226</v>
+        <v>JED1x57</v>
       </c>
       <c r="B233" t="str">
         <v>C</v>
@@ -4297,12 +4357,12 @@
         <v>335872</v>
       </c>
       <c r="E233" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>SYNHOST00227</v>
+        <v>CAI1x57</v>
       </c>
       <c r="B234" t="str">
         <v>C</v>
@@ -4314,12 +4374,12 @@
         <v>487424</v>
       </c>
       <c r="E234" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>SYNHOST00228</v>
+        <v>ALG1x57</v>
       </c>
       <c r="B235" t="str">
         <v>C</v>
@@ -4331,12 +4391,12 @@
         <v>377856</v>
       </c>
       <c r="E235" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>SYNHOST00229</v>
+        <v>TUN1x57</v>
       </c>
       <c r="B236" t="str">
         <v>C</v>
@@ -4348,12 +4408,12 @@
         <v>457728</v>
       </c>
       <c r="E236" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>SYNHOST00230</v>
+        <v>NBO1x57</v>
       </c>
       <c r="B237" t="str">
         <v>C</v>
@@ -4365,12 +4425,12 @@
         <v>252928</v>
       </c>
       <c r="E237" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>SYNHOST00231</v>
+        <v>JNB1x57</v>
       </c>
       <c r="B238" t="str">
         <v>C</v>
@@ -4382,12 +4442,12 @@
         <v>442368</v>
       </c>
       <c r="E238" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>SYNHOST00232</v>
+        <v>PEK1x57</v>
       </c>
       <c r="B239" t="str">
         <v>C</v>
@@ -4399,12 +4459,12 @@
         <v>402432</v>
       </c>
       <c r="E239" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>SYNHOST00233</v>
+        <v>PVG1x57</v>
       </c>
       <c r="B240" t="str">
         <v>C</v>
@@ -4416,12 +4476,12 @@
         <v>243712</v>
       </c>
       <c r="E240" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>SYNHOST00234</v>
+        <v>ICN1x57</v>
       </c>
       <c r="B241" t="str">
         <v>C</v>
@@ -4433,12 +4493,12 @@
         <v>285696</v>
       </c>
       <c r="E241" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>SYNHOST00235</v>
+        <v>NRT1x57</v>
       </c>
       <c r="B242" t="str">
         <v>C</v>
@@ -4450,12 +4510,12 @@
         <v>445440</v>
       </c>
       <c r="E242" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>SYNHOST00236</v>
+        <v>SIN1x57</v>
       </c>
       <c r="B243" t="str">
         <v>C</v>
@@ -4467,12 +4527,12 @@
         <v>209920</v>
       </c>
       <c r="E243" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>SYNHOST00237</v>
+        <v>BKK1x57</v>
       </c>
       <c r="B244" t="str">
         <v>C</v>
@@ -4484,12 +4544,12 @@
         <v>229376</v>
       </c>
       <c r="E244" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>SYNHOST00238</v>
+        <v>DEL1x57</v>
       </c>
       <c r="B245" t="str">
         <v>C</v>
@@ -4501,12 +4561,12 @@
         <v>505856</v>
       </c>
       <c r="E245" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>SYNHOST00239</v>
+        <v>BOM1x57</v>
       </c>
       <c r="B246" t="str">
         <v>C</v>
@@ -4518,12 +4578,12 @@
         <v>438272</v>
       </c>
       <c r="E246" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>SYNHOST00240</v>
+        <v>IST8x70</v>
       </c>
       <c r="B247" t="str">
         <v>C</v>
@@ -4535,12 +4595,12 @@
         <v>245760</v>
       </c>
       <c r="E247" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>SYNHOST00241</v>
+        <v>SAW8x70</v>
       </c>
       <c r="B248" t="str">
         <v>C</v>
@@ -4552,12 +4612,12 @@
         <v>442368</v>
       </c>
       <c r="E248" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>SYNHOST00242</v>
+        <v>ESB8x70</v>
       </c>
       <c r="B249" t="str">
         <v>C</v>
@@ -4569,12 +4629,12 @@
         <v>208896</v>
       </c>
       <c r="E249" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>SYNHOST00243</v>
+        <v>ADB8x70</v>
       </c>
       <c r="B250" t="str">
         <v>C</v>
@@ -4586,12 +4646,12 @@
         <v>420864</v>
       </c>
       <c r="E250" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>SYNHOST00244</v>
+        <v>AYT8x70</v>
       </c>
       <c r="B251" t="str">
         <v>C</v>
@@ -4603,12 +4663,12 @@
         <v>280576</v>
       </c>
       <c r="E251" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>SYNHOST00245</v>
+        <v>ADA8x70</v>
       </c>
       <c r="B252" t="str">
         <v>C</v>
@@ -4620,12 +4680,12 @@
         <v>456704</v>
       </c>
       <c r="E252" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>SYNHOST00246</v>
+        <v>TZX8x70</v>
       </c>
       <c r="B253" t="str">
         <v>C</v>
@@ -4637,12 +4697,12 @@
         <v>478208</v>
       </c>
       <c r="E253" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>SYNHOST00247</v>
+        <v>GZT8x70</v>
       </c>
       <c r="B254" t="str">
         <v>C</v>
@@ -4654,12 +4714,12 @@
         <v>347136</v>
       </c>
       <c r="E254" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>SYNHOST00248</v>
+        <v>KYA8x70</v>
       </c>
       <c r="B255" t="str">
         <v>C</v>
@@ -4671,12 +4731,12 @@
         <v>499712</v>
       </c>
       <c r="E255" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>SYNHOST00249</v>
+        <v>VAN8x70</v>
       </c>
       <c r="B256" t="str">
         <v>C</v>
@@ -4688,12 +4748,12 @@
         <v>421888</v>
       </c>
       <c r="E256" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>SYNHOST00250</v>
+        <v>JFK8x70</v>
       </c>
       <c r="B257" t="str">
         <v>C</v>
@@ -4705,12 +4765,12 @@
         <v>420864</v>
       </c>
       <c r="E257" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>SYNHOST00251</v>
+        <v>ORD8x70</v>
       </c>
       <c r="B258" t="str">
         <v>C</v>
@@ -4722,12 +4782,12 @@
         <v>279552</v>
       </c>
       <c r="E258" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>SYNHOST00252</v>
+        <v>IAD8x70</v>
       </c>
       <c r="B259" t="str">
         <v>C</v>
@@ -4739,12 +4799,12 @@
         <v>480256</v>
       </c>
       <c r="E259" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>SYNHOST00253</v>
+        <v>LAX8x70</v>
       </c>
       <c r="B260" t="str">
         <v>C</v>
@@ -4756,12 +4816,12 @@
         <v>473088</v>
       </c>
       <c r="E260" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>SYNHOST00254</v>
+        <v>MIA8x70</v>
       </c>
       <c r="B261" t="str">
         <v>C</v>
@@ -4773,12 +4833,12 @@
         <v>450560</v>
       </c>
       <c r="E261" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>SYNHOST00255</v>
+        <v>BOS8x70</v>
       </c>
       <c r="B262" t="str">
         <v>C</v>
@@ -4790,12 +4850,12 @@
         <v>501760</v>
       </c>
       <c r="E262" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>SYNHOST00256</v>
+        <v>LHR8x70</v>
       </c>
       <c r="B263" t="str">
         <v>C</v>
@@ -4807,12 +4867,12 @@
         <v>454656</v>
       </c>
       <c r="E263" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>SYNHOST00257</v>
+        <v>CDG8x70</v>
       </c>
       <c r="B264" t="str">
         <v>C</v>
@@ -4824,12 +4884,12 @@
         <v>286720</v>
       </c>
       <c r="E264" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>SYNHOST00258</v>
+        <v>FRA8x70</v>
       </c>
       <c r="B265" t="str">
         <v>C</v>
@@ -4841,12 +4901,12 @@
         <v>396288</v>
       </c>
       <c r="E265" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>SYNHOST00259</v>
+        <v>AMS8x70</v>
       </c>
       <c r="B266" t="str">
         <v>C</v>
@@ -4858,12 +4918,12 @@
         <v>450560</v>
       </c>
       <c r="E266" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>SYNHOST00260</v>
+        <v>MAD8x70</v>
       </c>
       <c r="B267" t="str">
         <v>C</v>
@@ -4875,12 +4935,12 @@
         <v>378880</v>
       </c>
       <c r="E267" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>SYNHOST00261</v>
+        <v>FCO8x70</v>
       </c>
       <c r="B268" t="str">
         <v>C</v>
@@ -4892,12 +4952,12 @@
         <v>391168</v>
       </c>
       <c r="E268" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>SYNHOST00262</v>
+        <v>MUC8x70</v>
       </c>
       <c r="B269" t="str">
         <v>C</v>
@@ -4909,12 +4969,12 @@
         <v>491520</v>
       </c>
       <c r="E269" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>SYNHOST00263</v>
+        <v>ZRH8x70</v>
       </c>
       <c r="B270" t="str">
         <v>C</v>
@@ -4926,12 +4986,12 @@
         <v>238592</v>
       </c>
       <c r="E270" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>SYNHOST00264</v>
+        <v>VIE8x70</v>
       </c>
       <c r="B271" t="str">
         <v>C</v>
@@ -4943,12 +5003,12 @@
         <v>212992</v>
       </c>
       <c r="E271" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>SYNHOST00265</v>
+        <v>BRU8x70</v>
       </c>
       <c r="B272" t="str">
         <v>C</v>
@@ -4960,12 +5020,12 @@
         <v>404480</v>
       </c>
       <c r="E272" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>SYNHOST00266</v>
+        <v>CPH8x70</v>
       </c>
       <c r="B273" t="str">
         <v>C</v>
@@ -4977,12 +5037,12 @@
         <v>436224</v>
       </c>
       <c r="E273" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>SYNHOST00267</v>
+        <v>ARN8x70</v>
       </c>
       <c r="B274" t="str">
         <v>C</v>
@@ -4994,12 +5054,12 @@
         <v>488448</v>
       </c>
       <c r="E274" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>SYNHOST00268</v>
+        <v>OSL8x70</v>
       </c>
       <c r="B275" t="str">
         <v>C</v>
@@ -5011,12 +5071,12 @@
         <v>402432</v>
       </c>
       <c r="E275" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>SYNHOST00269</v>
+        <v>WAW8x70</v>
       </c>
       <c r="B276" t="str">
         <v>C</v>
@@ -5028,12 +5088,12 @@
         <v>506880</v>
       </c>
       <c r="E276" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>SYNHOST00270</v>
+        <v>PRG8x70</v>
       </c>
       <c r="B277" t="str">
         <v>C</v>
@@ -5045,12 +5105,12 @@
         <v>260096</v>
       </c>
       <c r="E277" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>SYNHOST00271</v>
+        <v>BUD8x70</v>
       </c>
       <c r="B278" t="str">
         <v>C</v>
@@ -5062,12 +5122,12 @@
         <v>366592</v>
       </c>
       <c r="E278" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>SYNHOST00272</v>
+        <v>DXB8x70</v>
       </c>
       <c r="B279" t="str">
         <v>C</v>
@@ -5079,12 +5139,12 @@
         <v>333824</v>
       </c>
       <c r="E279" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>SYNHOST00273</v>
+        <v>DOH8x70</v>
       </c>
       <c r="B280" t="str">
         <v>C</v>
@@ -5096,12 +5156,12 @@
         <v>284672</v>
       </c>
       <c r="E280" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>SYNHOST00274</v>
+        <v>JED8x70</v>
       </c>
       <c r="B281" t="str">
         <v>C</v>
@@ -5113,12 +5173,12 @@
         <v>416768</v>
       </c>
       <c r="E281" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>SYNHOST00275</v>
+        <v>CAI8x70</v>
       </c>
       <c r="B282" t="str">
         <v>C</v>
@@ -5130,12 +5190,12 @@
         <v>274432</v>
       </c>
       <c r="E282" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>SYNHOST00276</v>
+        <v>ALG8x70</v>
       </c>
       <c r="B283" t="str">
         <v>C</v>
@@ -5147,12 +5207,12 @@
         <v>371712</v>
       </c>
       <c r="E283" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>SYNHOST00277</v>
+        <v>TUN8x70</v>
       </c>
       <c r="B284" t="str">
         <v>C</v>
@@ -5164,12 +5224,12 @@
         <v>431104</v>
       </c>
       <c r="E284" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>SYNHOST00278</v>
+        <v>NBO8x70</v>
       </c>
       <c r="B285" t="str">
         <v>C</v>
@@ -5181,12 +5241,12 @@
         <v>488448</v>
       </c>
       <c r="E285" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>SYNHOST00279</v>
+        <v>JNB8x70</v>
       </c>
       <c r="B286" t="str">
         <v>C</v>
@@ -5198,12 +5258,12 @@
         <v>347136</v>
       </c>
       <c r="E286" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>SYNHOST00280</v>
+        <v>PEK8x70</v>
       </c>
       <c r="B287" t="str">
         <v>C</v>
@@ -5215,12 +5275,12 @@
         <v>342016</v>
       </c>
       <c r="E287" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>SYNHOST00281</v>
+        <v>PVG8x70</v>
       </c>
       <c r="B288" t="str">
         <v>C</v>
@@ -5232,12 +5292,12 @@
         <v>257024</v>
       </c>
       <c r="E288" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>SYNHOST00282</v>
+        <v>ICN8x70</v>
       </c>
       <c r="B289" t="str">
         <v>C</v>
@@ -5249,12 +5309,12 @@
         <v>225280</v>
       </c>
       <c r="E289" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>SYNHOST00283</v>
+        <v>NRT8x70</v>
       </c>
       <c r="B290" t="str">
         <v>C</v>
@@ -5266,12 +5326,12 @@
         <v>351232</v>
       </c>
       <c r="E290" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>SYNHOST00284</v>
+        <v>SIN8x70</v>
       </c>
       <c r="B291" t="str">
         <v>C</v>
@@ -5283,12 +5343,12 @@
         <v>459776</v>
       </c>
       <c r="E291" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>SYNHOST00285</v>
+        <v>BKK8x70</v>
       </c>
       <c r="B292" t="str">
         <v>C</v>
@@ -5300,12 +5360,12 @@
         <v>234496</v>
       </c>
       <c r="E292" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>SYNHOST00286</v>
+        <v>DEL8x70</v>
       </c>
       <c r="B293" t="str">
         <v>C</v>
@@ -5317,12 +5377,12 @@
         <v>502784</v>
       </c>
       <c r="E293" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>SYNHOST00287</v>
+        <v>BOM8x70</v>
       </c>
       <c r="B294" t="str">
         <v>C</v>
@@ -5334,12 +5394,12 @@
         <v>446464</v>
       </c>
       <c r="E294" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>SYNHOST00288</v>
+        <v>IST5x83</v>
       </c>
       <c r="B295" t="str">
         <v>C</v>
@@ -5351,12 +5411,12 @@
         <v>271360</v>
       </c>
       <c r="E295" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>SYNHOST00289</v>
+        <v>SAW5x83</v>
       </c>
       <c r="B296" t="str">
         <v>C</v>
@@ -5368,12 +5428,12 @@
         <v>344064</v>
       </c>
       <c r="E296" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>SYNHOST00290</v>
+        <v>ESB5x83</v>
       </c>
       <c r="B297" t="str">
         <v>C</v>
@@ -5385,12 +5445,12 @@
         <v>247808</v>
       </c>
       <c r="E297" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>SYNHOST00291</v>
+        <v>ADB5x83</v>
       </c>
       <c r="B298" t="str">
         <v>C</v>
@@ -5402,12 +5462,12 @@
         <v>266240</v>
       </c>
       <c r="E298" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>SYNHOST00292</v>
+        <v>AYT5x83</v>
       </c>
       <c r="B299" t="str">
         <v>C</v>
@@ -5419,12 +5479,12 @@
         <v>497664</v>
       </c>
       <c r="E299" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>SYNHOST00293</v>
+        <v>ADA5x83</v>
       </c>
       <c r="B300" t="str">
         <v>C</v>
@@ -5436,12 +5496,12 @@
         <v>282624</v>
       </c>
       <c r="E300" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>SYNHOST00294</v>
+        <v>TZX5x83</v>
       </c>
       <c r="B301" t="str">
         <v>C</v>
@@ -5453,12 +5513,12 @@
         <v>294912</v>
       </c>
       <c r="E301" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>SYNHOST00295</v>
+        <v>GZT5x83</v>
       </c>
       <c r="B302" t="str">
         <v>C</v>
@@ -5470,12 +5530,12 @@
         <v>436224</v>
       </c>
       <c r="E302" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>SYNHOST00296</v>
+        <v>KYA5x83</v>
       </c>
       <c r="B303" t="str">
         <v>C</v>
@@ -5487,12 +5547,12 @@
         <v>472064</v>
       </c>
       <c r="E303" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>SYNHOST00297</v>
+        <v>VAN5x83</v>
       </c>
       <c r="B304" t="str">
         <v>C</v>
@@ -5504,12 +5564,12 @@
         <v>211968</v>
       </c>
       <c r="E304" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>SYNHOST00298</v>
+        <v>JFK5x83</v>
       </c>
       <c r="B305" t="str">
         <v>C</v>
@@ -5521,12 +5581,12 @@
         <v>329728</v>
       </c>
       <c r="E305" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>SYNHOST00299</v>
+        <v>ORD5x83</v>
       </c>
       <c r="B306" t="str">
         <v>C</v>
@@ -5538,12 +5598,12 @@
         <v>224256</v>
       </c>
       <c r="E306" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>SYNHOST00300</v>
+        <v>IAD5x83</v>
       </c>
       <c r="B307" t="str">
         <v>C</v>
@@ -5555,12 +5615,12 @@
         <v>427008</v>
       </c>
       <c r="E307" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>SYNHOST00301</v>
+        <v>LAX5x83</v>
       </c>
       <c r="B308" t="str">
         <v>C</v>
@@ -5572,12 +5632,12 @@
         <v>225280</v>
       </c>
       <c r="E308" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>SYNHOST00302</v>
+        <v>MIA5x83</v>
       </c>
       <c r="B309" t="str">
         <v>C</v>
@@ -5589,12 +5649,12 @@
         <v>340992</v>
       </c>
       <c r="E309" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>SYNHOST00303</v>
+        <v>BOS5x83</v>
       </c>
       <c r="B310" t="str">
         <v>C</v>
@@ -5606,12 +5666,12 @@
         <v>470016</v>
       </c>
       <c r="E310" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>SYNHOST00304</v>
+        <v>LHR5x83</v>
       </c>
       <c r="B311" t="str">
         <v>C</v>
@@ -5623,12 +5683,12 @@
         <v>457728</v>
       </c>
       <c r="E311" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>SYNHOST00305</v>
+        <v>CDG5x83</v>
       </c>
       <c r="B312" t="str">
         <v>C</v>
@@ -5640,12 +5700,12 @@
         <v>399360</v>
       </c>
       <c r="E312" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>SYNHOST00306</v>
+        <v>FRA5x83</v>
       </c>
       <c r="B313" t="str">
         <v>C</v>
@@ -5657,12 +5717,12 @@
         <v>216064</v>
       </c>
       <c r="E313" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>SYNHOST00307</v>
+        <v>AMS5x83</v>
       </c>
       <c r="B314" t="str">
         <v>C</v>
@@ -5674,12 +5734,12 @@
         <v>435200</v>
       </c>
       <c r="E314" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>SYNHOST00308</v>
+        <v>MAD5x83</v>
       </c>
       <c r="B315" t="str">
         <v>C</v>
@@ -5691,12 +5751,12 @@
         <v>353280</v>
       </c>
       <c r="E315" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>SYNHOST00309</v>
+        <v>FCO5x83</v>
       </c>
       <c r="B316" t="str">
         <v>C</v>
@@ -5708,12 +5768,12 @@
         <v>397312</v>
       </c>
       <c r="E316" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>SYNHOST00310</v>
+        <v>MUC5x83</v>
       </c>
       <c r="B317" t="str">
         <v>C</v>
@@ -5725,12 +5785,12 @@
         <v>483328</v>
       </c>
       <c r="E317" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>SYNHOST00311</v>
+        <v>ZRH5x83</v>
       </c>
       <c r="B318" t="str">
         <v>C</v>
@@ -5742,12 +5802,12 @@
         <v>294912</v>
       </c>
       <c r="E318" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>SYNHOST00312</v>
+        <v>VIE5x83</v>
       </c>
       <c r="B319" t="str">
         <v>C</v>
@@ -5759,12 +5819,12 @@
         <v>397312</v>
       </c>
       <c r="E319" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>SYNHOST00313</v>
+        <v>BRU5x83</v>
       </c>
       <c r="B320" t="str">
         <v>C</v>
@@ -5776,12 +5836,12 @@
         <v>291840</v>
       </c>
       <c r="E320" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>SYNHOST00314</v>
+        <v>CPH5x83</v>
       </c>
       <c r="B321" t="str">
         <v>C</v>
@@ -5793,12 +5853,12 @@
         <v>413696</v>
       </c>
       <c r="E321" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>SYNHOST00315</v>
+        <v>ARN5x83</v>
       </c>
       <c r="B322" t="str">
         <v>C</v>
@@ -5810,12 +5870,12 @@
         <v>385024</v>
       </c>
       <c r="E322" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>SYNHOST00316</v>
+        <v>OSL5x83</v>
       </c>
       <c r="B323" t="str">
         <v>C</v>
@@ -5827,12 +5887,12 @@
         <v>275456</v>
       </c>
       <c r="E323" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>SYNHOST00317</v>
+        <v>WAW5x83</v>
       </c>
       <c r="B324" t="str">
         <v>C</v>
@@ -5844,12 +5904,12 @@
         <v>357376</v>
       </c>
       <c r="E324" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>SYNHOST00318</v>
+        <v>PRG5x83</v>
       </c>
       <c r="B325" t="str">
         <v>C</v>
@@ -5861,12 +5921,12 @@
         <v>388096</v>
       </c>
       <c r="E325" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>SYNHOST00319</v>
+        <v>BUD5x83</v>
       </c>
       <c r="B326" t="str">
         <v>C</v>
@@ -5878,12 +5938,12 @@
         <v>282624</v>
       </c>
       <c r="E326" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>SYNHOST00320</v>
+        <v>DXB5x83</v>
       </c>
       <c r="B327" t="str">
         <v>C</v>
@@ -5895,12 +5955,12 @@
         <v>342016</v>
       </c>
       <c r="E327" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>SYNHOST00321</v>
+        <v>DOH5x83</v>
       </c>
       <c r="B328" t="str">
         <v>C</v>
@@ -5912,12 +5972,12 @@
         <v>377856</v>
       </c>
       <c r="E328" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>SYNHOST00322</v>
+        <v>JED5x83</v>
       </c>
       <c r="B329" t="str">
         <v>C</v>
@@ -5929,12 +5989,12 @@
         <v>481280</v>
       </c>
       <c r="E329" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>SYNHOST00323</v>
+        <v>CAI5x83</v>
       </c>
       <c r="B330" t="str">
         <v>C</v>
@@ -5946,12 +6006,12 @@
         <v>386048</v>
       </c>
       <c r="E330" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>SYNHOST00324</v>
+        <v>ALG5x83</v>
       </c>
       <c r="B331" t="str">
         <v>C</v>
@@ -5963,12 +6023,12 @@
         <v>432128</v>
       </c>
       <c r="E331" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>SYNHOST00325</v>
+        <v>TUN5x83</v>
       </c>
       <c r="B332" t="str">
         <v>C</v>
@@ -5980,12 +6040,12 @@
         <v>407552</v>
       </c>
       <c r="E332" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>SYNHOST00326</v>
+        <v>NBO5x83</v>
       </c>
       <c r="B333" t="str">
         <v>C</v>
@@ -5997,12 +6057,12 @@
         <v>291840</v>
       </c>
       <c r="E333" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>SYNHOST00327</v>
+        <v>JNB5x83</v>
       </c>
       <c r="B334" t="str">
         <v>C</v>
@@ -6014,12 +6074,12 @@
         <v>327680</v>
       </c>
       <c r="E334" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>SYNHOST00328</v>
+        <v>PEK5x83</v>
       </c>
       <c r="B335" t="str">
         <v>C</v>
@@ -6031,12 +6091,12 @@
         <v>209920</v>
       </c>
       <c r="E335" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>SYNHOST00329</v>
+        <v>PVG5x83</v>
       </c>
       <c r="B336" t="str">
         <v>C</v>
@@ -6048,12 +6108,12 @@
         <v>333824</v>
       </c>
       <c r="E336" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>SYNHOST00330</v>
+        <v>ICN5x83</v>
       </c>
       <c r="B337" t="str">
         <v>C</v>
@@ -6065,12 +6125,12 @@
         <v>352256</v>
       </c>
       <c r="E337" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>SYNHOST00331</v>
+        <v>NRT5x83</v>
       </c>
       <c r="B338" t="str">
         <v>C</v>
@@ -6082,12 +6142,12 @@
         <v>320512</v>
       </c>
       <c r="E338" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>SYNHOST00332</v>
+        <v>SIN5x83</v>
       </c>
       <c r="B339" t="str">
         <v>C</v>
@@ -6099,12 +6159,12 @@
         <v>336896</v>
       </c>
       <c r="E339" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>SYNHOST00333</v>
+        <v>BKK5x83</v>
       </c>
       <c r="B340" t="str">
         <v>C</v>
@@ -6116,12 +6176,12 @@
         <v>295936</v>
       </c>
       <c r="E340" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>SYNHOST00334</v>
+        <v>DEL5x83</v>
       </c>
       <c r="B341" t="str">
         <v>C</v>
@@ -6133,12 +6193,12 @@
         <v>310272</v>
       </c>
       <c r="E341" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>SYNHOST00335</v>
+        <v>BOM5x83</v>
       </c>
       <c r="B342" t="str">
         <v>C</v>
@@ -6150,12 +6210,12 @@
         <v>436224</v>
       </c>
       <c r="E342" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>SYNHOST00336</v>
+        <v>IST2x96</v>
       </c>
       <c r="B343" t="str">
         <v>C</v>
@@ -6167,12 +6227,12 @@
         <v>267264</v>
       </c>
       <c r="E343" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>SYNHOST00337</v>
+        <v>SAW2x96</v>
       </c>
       <c r="B344" t="str">
         <v>C</v>
@@ -6184,12 +6244,12 @@
         <v>498688</v>
       </c>
       <c r="E344" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>SYNHOST00338</v>
+        <v>ESB2x96</v>
       </c>
       <c r="B345" t="str">
         <v>C</v>
@@ -6201,12 +6261,12 @@
         <v>453632</v>
       </c>
       <c r="E345" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>SYNHOST00339</v>
+        <v>ADB2x96</v>
       </c>
       <c r="B346" t="str">
         <v>C</v>
@@ -6218,12 +6278,12 @@
         <v>372736</v>
       </c>
       <c r="E346" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>SYNHOST00340</v>
+        <v>AYT2x96</v>
       </c>
       <c r="B347" t="str">
         <v>C</v>
@@ -6235,12 +6295,12 @@
         <v>388096</v>
       </c>
       <c r="E347" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>SYNHOST00341</v>
+        <v>ADA2x96</v>
       </c>
       <c r="B348" t="str">
         <v>C</v>
@@ -6252,12 +6312,12 @@
         <v>339968</v>
       </c>
       <c r="E348" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>SYNHOST00342</v>
+        <v>TZX2x96</v>
       </c>
       <c r="B349" t="str">
         <v>C</v>
@@ -6269,12 +6329,12 @@
         <v>402432</v>
       </c>
       <c r="E349" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>SYNHOST00343</v>
+        <v>GZT2x96</v>
       </c>
       <c r="B350" t="str">
         <v>C</v>
@@ -6286,12 +6346,12 @@
         <v>367616</v>
       </c>
       <c r="E350" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>SYNHOST00344</v>
+        <v>KYA2x96</v>
       </c>
       <c r="B351" t="str">
         <v>C</v>
@@ -6303,12 +6363,12 @@
         <v>491520</v>
       </c>
       <c r="E351" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>SYNHOST00345</v>
+        <v>VAN2x96</v>
       </c>
       <c r="B352" t="str">
         <v>C</v>
@@ -6320,12 +6380,12 @@
         <v>335872</v>
       </c>
       <c r="E352" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>SYNHOST00346</v>
+        <v>JFK2x96</v>
       </c>
       <c r="B353" t="str">
         <v>C</v>
@@ -6337,12 +6397,12 @@
         <v>230400</v>
       </c>
       <c r="E353" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>SYNHOST00347</v>
+        <v>ORD2x96</v>
       </c>
       <c r="B354" t="str">
         <v>C</v>
@@ -6354,12 +6414,12 @@
         <v>362496</v>
       </c>
       <c r="E354" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>SYNHOST00348</v>
+        <v>IAD2x96</v>
       </c>
       <c r="B355" t="str">
         <v>C</v>
@@ -6371,12 +6431,12 @@
         <v>308224</v>
       </c>
       <c r="E355" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>SYNHOST00349</v>
+        <v>LAX2x96</v>
       </c>
       <c r="B356" t="str">
         <v>C</v>
@@ -6388,12 +6448,12 @@
         <v>430080</v>
       </c>
       <c r="E356" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>SYNHOST00350</v>
+        <v>MIA2x96</v>
       </c>
       <c r="B357" t="str">
         <v>C</v>
@@ -6405,12 +6465,12 @@
         <v>501760</v>
       </c>
       <c r="E357" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>SYNHOST00351</v>
+        <v>BOS2x96</v>
       </c>
       <c r="B358" t="str">
         <v>C</v>
@@ -6422,12 +6482,12 @@
         <v>420864</v>
       </c>
       <c r="E358" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>SYNHOST00352</v>
+        <v>LHR2x96</v>
       </c>
       <c r="B359" t="str">
         <v>C</v>
@@ -6439,12 +6499,12 @@
         <v>273408</v>
       </c>
       <c r="E359" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>SYNHOST00353</v>
+        <v>CDG2x96</v>
       </c>
       <c r="B360" t="str">
         <v>C</v>
@@ -6456,12 +6516,12 @@
         <v>270336</v>
       </c>
       <c r="E360" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>SYNHOST00354</v>
+        <v>FRA2x96</v>
       </c>
       <c r="B361" t="str">
         <v>C</v>
@@ -6473,12 +6533,12 @@
         <v>358400</v>
       </c>
       <c r="E361" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>SYNHOST00355</v>
+        <v>AMS2x96</v>
       </c>
       <c r="B362" t="str">
         <v>C</v>
@@ -6490,12 +6550,12 @@
         <v>240640</v>
       </c>
       <c r="E362" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>SYNHOST00356</v>
+        <v>MAD2x96</v>
       </c>
       <c r="B363" t="str">
         <v>C</v>
@@ -6507,12 +6567,12 @@
         <v>462848</v>
       </c>
       <c r="E363" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>SYNHOST00357</v>
+        <v>FCO2x96</v>
       </c>
       <c r="B364" t="str">
         <v>C</v>
@@ -6524,12 +6584,12 @@
         <v>239616</v>
       </c>
       <c r="E364" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>SYNHOST00358</v>
+        <v>MUC2x96</v>
       </c>
       <c r="B365" t="str">
         <v>C</v>
@@ -6541,12 +6601,12 @@
         <v>343040</v>
       </c>
       <c r="E365" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>SYNHOST00359</v>
+        <v>ZRH2x96</v>
       </c>
       <c r="B366" t="str">
         <v>C</v>
@@ -6558,12 +6618,12 @@
         <v>354304</v>
       </c>
       <c r="E366" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>SYNHOST00360</v>
+        <v>VIE2x96</v>
       </c>
       <c r="B367" t="str">
         <v>C</v>
@@ -6575,12 +6635,12 @@
         <v>364544</v>
       </c>
       <c r="E367" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>SYNHOST00361</v>
+        <v>BRU2x96</v>
       </c>
       <c r="B368" t="str">
         <v>C</v>
@@ -6592,12 +6652,12 @@
         <v>427008</v>
       </c>
       <c r="E368" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>SYNHOST00362</v>
+        <v>CPH2x96</v>
       </c>
       <c r="B369" t="str">
         <v>C</v>
@@ -6609,12 +6669,12 @@
         <v>453632</v>
       </c>
       <c r="E369" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>SYNHOST00363</v>
+        <v>ARN2x96</v>
       </c>
       <c r="B370" t="str">
         <v>C</v>
@@ -6626,12 +6686,12 @@
         <v>228352</v>
       </c>
       <c r="E370" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>SYNHOST00364</v>
+        <v>OSL2x96</v>
       </c>
       <c r="B371" t="str">
         <v>C</v>
@@ -6643,12 +6703,12 @@
         <v>468992</v>
       </c>
       <c r="E371" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>SYNHOST00365</v>
+        <v>WAW2x96</v>
       </c>
       <c r="B372" t="str">
         <v>C</v>
@@ -6660,12 +6720,12 @@
         <v>332800</v>
       </c>
       <c r="E372" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>SYNHOST00366</v>
+        <v>PRG2x96</v>
       </c>
       <c r="B373" t="str">
         <v>C</v>
@@ -6677,12 +6737,12 @@
         <v>498688</v>
       </c>
       <c r="E373" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>SYNHOST00367</v>
+        <v>BUD2x96</v>
       </c>
       <c r="B374" t="str">
         <v>C</v>
@@ -6694,12 +6754,12 @@
         <v>342016</v>
       </c>
       <c r="E374" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>SYNHOST00368</v>
+        <v>DXB2x96</v>
       </c>
       <c r="B375" t="str">
         <v>C</v>
@@ -6711,12 +6771,12 @@
         <v>234496</v>
       </c>
       <c r="E375" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>SYNHOST00369</v>
+        <v>DOH2x96</v>
       </c>
       <c r="B376" t="str">
         <v>C</v>
@@ -6728,12 +6788,12 @@
         <v>237568</v>
       </c>
       <c r="E376" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>SYNHOST00370</v>
+        <v>JED2x96</v>
       </c>
       <c r="B377" t="str">
         <v>C</v>
@@ -6745,12 +6805,12 @@
         <v>492544</v>
       </c>
       <c r="E377" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>SYNHOST00371</v>
+        <v>CAI2x96</v>
       </c>
       <c r="B378" t="str">
         <v>C</v>
@@ -6762,12 +6822,12 @@
         <v>484352</v>
       </c>
       <c r="E378" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>SYNHOST00372</v>
+        <v>ALG2x96</v>
       </c>
       <c r="B379" t="str">
         <v>C</v>
@@ -6779,12 +6839,12 @@
         <v>349184</v>
       </c>
       <c r="E379" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>SYNHOST00373</v>
+        <v>TUN2x96</v>
       </c>
       <c r="B380" t="str">
         <v>C</v>
@@ -6796,12 +6856,12 @@
         <v>291840</v>
       </c>
       <c r="E380" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>SYNHOST00374</v>
+        <v>NBO2x96</v>
       </c>
       <c r="B381" t="str">
         <v>C</v>
@@ -6813,12 +6873,12 @@
         <v>457728</v>
       </c>
       <c r="E381" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>SYNHOST00375</v>
+        <v>JNB2x96</v>
       </c>
       <c r="B382" t="str">
         <v>C</v>
@@ -6830,12 +6890,12 @@
         <v>465920</v>
       </c>
       <c r="E382" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>SYNHOST00376</v>
+        <v>PEK2x96</v>
       </c>
       <c r="B383" t="str">
         <v>C</v>
@@ -6847,12 +6907,12 @@
         <v>392192</v>
       </c>
       <c r="E383" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>SYNHOST00377</v>
+        <v>PVG2x96</v>
       </c>
       <c r="B384" t="str">
         <v>C</v>
@@ -6864,12 +6924,12 @@
         <v>265216</v>
       </c>
       <c r="E384" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>SYNHOST00378</v>
+        <v>ICN2x96</v>
       </c>
       <c r="B385" t="str">
         <v>C</v>
@@ -6881,12 +6941,12 @@
         <v>230400</v>
       </c>
       <c r="E385" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>SYNHOST00379</v>
+        <v>NRT2x96</v>
       </c>
       <c r="B386" t="str">
         <v>C</v>
@@ -6898,12 +6958,12 @@
         <v>243712</v>
       </c>
       <c r="E386" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>SYNHOST00380</v>
+        <v>SIN2x96</v>
       </c>
       <c r="B387" t="str">
         <v>C</v>
@@ -6915,12 +6975,12 @@
         <v>306176</v>
       </c>
       <c r="E387" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>SYNHOST00381</v>
+        <v>BKK2x96</v>
       </c>
       <c r="B388" t="str">
         <v>C</v>
@@ -6932,12 +6992,12 @@
         <v>398336</v>
       </c>
       <c r="E388" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>SYNHOST00382</v>
+        <v>DEL2x96</v>
       </c>
       <c r="B389" t="str">
         <v>C</v>
@@ -6949,12 +7009,12 @@
         <v>474112</v>
       </c>
       <c r="E389" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>SYNHOST00383</v>
+        <v>BOM2x96</v>
       </c>
       <c r="B390" t="str">
         <v>C</v>
@@ -6966,12 +7026,12 @@
         <v>300032</v>
       </c>
       <c r="E390" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>SYNHOST00384</v>
+        <v>IST9x09</v>
       </c>
       <c r="B391" t="str">
         <v>C</v>
@@ -6983,12 +7043,12 @@
         <v>245760</v>
       </c>
       <c r="E391" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>SYNHOST00385</v>
+        <v>SAW9x09</v>
       </c>
       <c r="B392" t="str">
         <v>C</v>
@@ -7000,12 +7060,12 @@
         <v>318464</v>
       </c>
       <c r="E392" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>SYNHOST00386</v>
+        <v>ESB9x09</v>
       </c>
       <c r="B393" t="str">
         <v>C</v>
@@ -7017,12 +7077,12 @@
         <v>294912</v>
       </c>
       <c r="E393" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>SYNHOST00387</v>
+        <v>ADB9x09</v>
       </c>
       <c r="B394" t="str">
         <v>C</v>
@@ -7034,12 +7094,12 @@
         <v>505856</v>
       </c>
       <c r="E394" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>SYNHOST00388</v>
+        <v>AYT9x09</v>
       </c>
       <c r="B395" t="str">
         <v>C</v>
@@ -7051,12 +7111,12 @@
         <v>398336</v>
       </c>
       <c r="E395" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>SYNHOST00389</v>
+        <v>ADA9x09</v>
       </c>
       <c r="B396" t="str">
         <v>C</v>
@@ -7068,12 +7128,12 @@
         <v>357376</v>
       </c>
       <c r="E396" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>SYNHOST00390</v>
+        <v>TZX9x09</v>
       </c>
       <c r="B397" t="str">
         <v>C</v>
@@ -7085,12 +7145,12 @@
         <v>284672</v>
       </c>
       <c r="E397" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>SYNHOST00391</v>
+        <v>GZT9x09</v>
       </c>
       <c r="B398" t="str">
         <v>C</v>
@@ -7102,12 +7162,12 @@
         <v>275456</v>
       </c>
       <c r="E398" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>SYNHOST00392</v>
+        <v>KYA9x09</v>
       </c>
       <c r="B399" t="str">
         <v>C</v>
@@ -7119,12 +7179,12 @@
         <v>463872</v>
       </c>
       <c r="E399" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>SYNHOST00393</v>
+        <v>VAN9x09</v>
       </c>
       <c r="B400" t="str">
         <v>C</v>
@@ -7136,12 +7196,12 @@
         <v>335872</v>
       </c>
       <c r="E400" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>SYNHOST00394</v>
+        <v>JFK9x09</v>
       </c>
       <c r="B401" t="str">
         <v>C</v>
@@ -7153,12 +7213,12 @@
         <v>335872</v>
       </c>
       <c r="E401" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>SYNHOST00395</v>
+        <v>ORD9x09</v>
       </c>
       <c r="B402" t="str">
         <v>C</v>
@@ -7170,12 +7230,12 @@
         <v>484352</v>
       </c>
       <c r="E402" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>SYNHOST00396</v>
+        <v>IAD9x09</v>
       </c>
       <c r="B403" t="str">
         <v>C</v>
@@ -7187,12 +7247,12 @@
         <v>337920</v>
       </c>
       <c r="E403" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>SYNHOST00397</v>
+        <v>LAX9x09</v>
       </c>
       <c r="B404" t="str">
         <v>C</v>
@@ -7204,12 +7264,12 @@
         <v>339968</v>
       </c>
       <c r="E404" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>SYNHOST00398</v>
+        <v>MIA9x09</v>
       </c>
       <c r="B405" t="str">
         <v>C</v>
@@ -7221,12 +7281,12 @@
         <v>249856</v>
       </c>
       <c r="E405" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>SYNHOST00399</v>
+        <v>BOS9x09</v>
       </c>
       <c r="B406" t="str">
         <v>C</v>
@@ -7238,7 +7298,7 @@
         <v>332800</v>
       </c>
       <c r="E406" t="str">
-        <v>SYN</v>
+        <v>IST</v>
       </c>
     </row>
   </sheetData>
